--- a/nriss-patch-2/ig/all-profiles.xlsx
+++ b/nriss-patch-2/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T15:04:42+00:00</t>
+    <t>2026-04-22T16:14:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -809,7 +809,7 @@
 </t>
   </si>
   <si>
-    <t>Cet attribut représente l’acteur validant le document et prenant la responsabilité du contenu médical de celui-ci. Il peut s’agir de l’auteur du document si celui-ci est une personne et s’il endosse la responsabilité du contenu médical de ses documents. Si l’auteur est un dispositif, cet attribut doit représenter la personne responsable de l’action effectuée par le dispositif. Pour les documents d’expression personnelle du patient, cet attribut fait référence au patient.</t>
+    <t>Cet attribut représente l’acteur validant le document et prenant la responsabilité du contenu médical de celui-ci. Il peut s’agir de l’auteur du document si celui-ci est une personne et s’il endosse la responsabilité du contenu médical de ses documents. Si l’auteur est un dispositif, cet attribut doit représenter l'organisation responsable de l’action effectuée par le dispositif. Dans le cas où le document est poussé par le patient, l'authenticator doit rester vide.</t>
   </si>
   <si>
     <t>Which person or organization authenticates that this document is valid.</t>

--- a/nriss-patch-2/ig/all-profiles.xlsx
+++ b/nriss-patch-2/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T16:14:13+00:00</t>
+    <t>2026-04-22T16:17:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -809,7 +809,7 @@
 </t>
   </si>
   <si>
-    <t>Cet attribut représente l’acteur validant le document et prenant la responsabilité du contenu médical de celui-ci. Il peut s’agir de l’auteur du document si celui-ci est une personne et s’il endosse la responsabilité du contenu médical de ses documents. Si l’auteur est un dispositif, cet attribut doit représenter l'organisation responsable de l’action effectuée par le dispositif. Dans le cas où le document est poussé par le patient, l'authenticator doit rester vide.</t>
+    <t>Cet attribut représente l’acteur validant le document et prenant la responsabilité du contenu médical de celui-ci. Il peut s’agir de l’auteur du document si celui-ci est une personne et s’il endosse la responsabilité du contenu médical de ses documents. Si l’auteur est un dispositif, cet attribut doit représenter l'organisation responsable de l’action effectuée par le dispositif. L'authenticator DOIT être renseigné, sauf dans le cas où le document est une expression personnelle du patient, auquel cas l'authenticator doit rester vide.</t>
   </si>
   <si>
     <t>Which person or organization authenticates that this document is valid.</t>

--- a/nriss-patch-2/ig/all-profiles.xlsx
+++ b/nriss-patch-2/ig/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24995" uniqueCount="1336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24995" uniqueCount="1335">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T16:17:14+00:00</t>
+    <t>2026-05-27T14:01:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -809,7 +809,7 @@
 </t>
   </si>
   <si>
-    <t>Cet attribut représente l’acteur validant le document et prenant la responsabilité du contenu médical de celui-ci. Il peut s’agir de l’auteur du document si celui-ci est une personne et s’il endosse la responsabilité du contenu médical de ses documents. Si l’auteur est un dispositif, cet attribut doit représenter l'organisation responsable de l’action effectuée par le dispositif. L'authenticator DOIT être renseigné, sauf dans le cas où le document est une expression personnelle du patient, auquel cas l'authenticator doit rester vide.</t>
+    <t>Cet attribut représente l’acteur validant le document et prenant la responsabilité du contenu médical de celui-ci. Il peut s’agir de l’auteur du document si celui-ci est une personne et s’il endosse la responsabilité du contenu médical de ses documents.</t>
   </si>
   <si>
     <t>Which person or organization authenticates that this document is valid.</t>
@@ -3895,9 +3895,6 @@
   <si>
     <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization)
 </t>
-  </si>
-  <si>
-    <t>Cet attribut représente l’acteur validant le document et prenant la responsabilité du contenu médical de celui-ci. Il peut s’agir de l’auteur du document si celui-ci est une personne et s’il endosse la responsabilité du contenu médical de ses documents. Si l’auteur est un dispositif, cet attribut doit représenter la personne responsable de l’action effectuée par le dispositif.</t>
   </si>
   <si>
     <t>Relationships to other documents</t>
@@ -5666,7 +5663,7 @@
         <v>2</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="174">
@@ -5674,7 +5671,7 @@
         <v>4</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="175">
@@ -5690,7 +5687,7 @@
         <v>8</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="177">
@@ -5698,7 +5695,7 @@
         <v>10</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>1257</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="178">
@@ -5752,7 +5749,7 @@
         <v>23</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="185">
@@ -5796,7 +5793,7 @@
         <v>33</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>1259</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="191">
@@ -73760,7 +73757,7 @@
         <v>1243</v>
       </c>
       <c r="M651" t="s" s="2">
-        <v>1244</v>
+        <v>250</v>
       </c>
       <c r="N651" t="s" s="2">
         <v>251</v>
@@ -73970,10 +73967,10 @@
         <v>259</v>
       </c>
       <c r="M653" t="s" s="2">
+        <v>1244</v>
+      </c>
+      <c r="N653" t="s" s="2">
         <v>1245</v>
-      </c>
-      <c r="N653" t="s" s="2">
-        <v>1246</v>
       </c>
       <c r="O653" t="s" s="2">
         <v>262</v>
@@ -74390,7 +74387,7 @@
         <v>159</v>
       </c>
       <c r="M657" t="s" s="2">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="N657" t="s" s="2">
         <v>274</v>
@@ -74495,7 +74492,7 @@
         <v>279</v>
       </c>
       <c r="M658" t="s" s="2">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="N658" t="s" s="2">
         <v>281</v>
@@ -74812,7 +74809,7 @@
         <v>259</v>
       </c>
       <c r="M661" t="s" s="2">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="N661" t="s" s="2">
         <v>296</v>
@@ -75751,7 +75748,7 @@
         <v>321</v>
       </c>
       <c r="M670" t="s" s="2">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="N670" t="s" s="2">
         <v>323</v>
@@ -75858,7 +75855,7 @@
         <v>328</v>
       </c>
       <c r="M671" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="N671" t="s" s="2">
         <v>330</v>
@@ -76284,7 +76281,7 @@
         <v>356</v>
       </c>
       <c r="M675" t="s" s="2">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="N675" t="s" s="2">
         <v>358</v>
@@ -77287,7 +77284,7 @@
         <v>75</v>
       </c>
       <c r="AK684" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="685">
@@ -77392,7 +77389,7 @@
         <v>75</v>
       </c>
       <c r="AK685" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="686">
@@ -77605,7 +77602,7 @@
     </row>
     <row r="688">
       <c r="A688" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B688" t="s" s="2">
         <v>1099</v>
@@ -77708,7 +77705,7 @@
     </row>
     <row r="689">
       <c r="A689" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B689" t="s" s="2">
         <v>1101</v>
@@ -77813,7 +77810,7 @@
     </row>
     <row r="690">
       <c r="A690" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B690" t="s" s="2">
         <v>1102</v>
@@ -77916,7 +77913,7 @@
     </row>
     <row r="691">
       <c r="A691" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B691" t="s" s="2">
         <v>1103</v>
@@ -78019,7 +78016,7 @@
     </row>
     <row r="692">
       <c r="A692" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B692" t="s" s="2">
         <v>1104</v>
@@ -78124,7 +78121,7 @@
     </row>
     <row r="693">
       <c r="A693" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B693" t="s" s="2">
         <v>1105</v>
@@ -78229,7 +78226,7 @@
     </row>
     <row r="694">
       <c r="A694" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B694" t="s" s="2">
         <v>1106</v>
@@ -78334,7 +78331,7 @@
     </row>
     <row r="695">
       <c r="A695" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B695" t="s" s="2">
         <v>1107</v>
@@ -78439,7 +78436,7 @@
     </row>
     <row r="696">
       <c r="A696" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B696" t="s" s="2">
         <v>1108</v>
@@ -78544,7 +78541,7 @@
     </row>
     <row r="697">
       <c r="A697" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B697" t="s" s="2">
         <v>1109</v>
@@ -78649,7 +78646,7 @@
     </row>
     <row r="698">
       <c r="A698" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B698" t="s" s="2">
         <v>1110</v>
@@ -78754,7 +78751,7 @@
     </row>
     <row r="699">
       <c r="A699" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B699" t="s" s="2">
         <v>1111</v>
@@ -78859,7 +78856,7 @@
     </row>
     <row r="700">
       <c r="A700" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B700" t="s" s="2">
         <v>1112</v>
@@ -78964,7 +78961,7 @@
     </row>
     <row r="701">
       <c r="A701" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B701" t="s" s="2">
         <v>1113</v>
@@ -79069,7 +79066,7 @@
     </row>
     <row r="702">
       <c r="A702" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B702" t="s" s="2">
         <v>1114</v>
@@ -79101,7 +79098,7 @@
         <v>176</v>
       </c>
       <c r="M702" t="s" s="2">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="N702" t="s" s="2">
         <v>178</v>
@@ -79174,7 +79171,7 @@
     </row>
     <row r="703">
       <c r="A703" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B703" t="s" s="2">
         <v>1116</v>
@@ -79188,7 +79185,7 @@
       </c>
       <c r="F703" s="2"/>
       <c r="G703" t="s" s="2">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="H703" t="s" s="2">
         <v>77</v>
@@ -79275,7 +79272,7 @@
     </row>
     <row r="704">
       <c r="A704" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B704" t="s" s="2">
         <v>1117</v>
@@ -79309,7 +79306,7 @@
         <v>1119</v>
       </c>
       <c r="M704" t="s" s="2">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="N704" t="s" s="2">
         <v>1121</v>
@@ -79375,18 +79372,18 @@
         <v>190</v>
       </c>
       <c r="AK704" t="s" s="2">
-        <v>1263</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B705" t="s" s="2">
+        <v>1263</v>
+      </c>
+      <c r="C705" t="s" s="2">
         <v>1264</v>
-      </c>
-      <c r="C705" t="s" s="2">
-        <v>1265</v>
       </c>
       <c r="D705" s="2"/>
       <c r="E705" t="s" s="2">
@@ -79483,13 +79480,13 @@
     </row>
     <row r="706">
       <c r="A706" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B706" t="s" s="2">
+        <v>1265</v>
+      </c>
+      <c r="C706" t="s" s="2">
         <v>1266</v>
-      </c>
-      <c r="C706" t="s" s="2">
-        <v>1267</v>
       </c>
       <c r="D706" s="2"/>
       <c r="E706" t="s" s="2">
@@ -79586,13 +79583,13 @@
     </row>
     <row r="707">
       <c r="A707" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B707" t="s" s="2">
+        <v>1267</v>
+      </c>
+      <c r="C707" t="s" s="2">
         <v>1268</v>
-      </c>
-      <c r="C707" t="s" s="2">
-        <v>1269</v>
       </c>
       <c r="D707" s="2"/>
       <c r="E707" t="s" s="2">
@@ -79632,7 +79629,7 @@
       </c>
       <c r="R707" s="2"/>
       <c r="S707" t="s" s="2">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="T707" t="s" s="2">
         <v>75</v>
@@ -79691,13 +79688,13 @@
     </row>
     <row r="708">
       <c r="A708" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B708" t="s" s="2">
+        <v>1270</v>
+      </c>
+      <c r="C708" t="s" s="2">
         <v>1271</v>
-      </c>
-      <c r="C708" t="s" s="2">
-        <v>1272</v>
       </c>
       <c r="D708" s="2"/>
       <c r="E708" t="s" s="2">
@@ -79757,13 +79754,13 @@
       </c>
       <c r="Z708" s="2"/>
       <c r="AA708" t="s" s="2">
+        <v>1272</v>
+      </c>
+      <c r="AB708" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC708" t="s" s="2">
         <v>1273</v>
-      </c>
-      <c r="AB708" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC708" t="s" s="2">
-        <v>1274</v>
       </c>
       <c r="AD708" s="2"/>
       <c r="AE708" t="s" s="2">
@@ -79790,16 +79787,16 @@
     </row>
     <row r="709">
       <c r="A709" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B709" t="s" s="2">
+        <v>1274</v>
+      </c>
+      <c r="C709" t="s" s="2">
+        <v>1271</v>
+      </c>
+      <c r="D709" t="s" s="2">
         <v>1275</v>
-      </c>
-      <c r="C709" t="s" s="2">
-        <v>1272</v>
-      </c>
-      <c r="D709" t="s" s="2">
-        <v>1276</v>
       </c>
       <c r="E709" t="s" s="2">
         <v>75</v>
@@ -79895,16 +79892,16 @@
     </row>
     <row r="710">
       <c r="A710" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B710" t="s" s="2">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="C710" t="s" s="2">
         <v>1116</v>
       </c>
       <c r="D710" t="s" s="2">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="E710" t="s" s="2">
         <v>75</v>
@@ -79926,13 +79923,13 @@
         <v>75</v>
       </c>
       <c r="L710" t="s" s="2">
+        <v>1278</v>
+      </c>
+      <c r="M710" t="s" s="2">
         <v>1279</v>
       </c>
-      <c r="M710" t="s" s="2">
+      <c r="N710" t="s" s="2">
         <v>1280</v>
-      </c>
-      <c r="N710" t="s" s="2">
-        <v>1281</v>
       </c>
       <c r="O710" s="2"/>
       <c r="P710" s="2"/>
@@ -80000,16 +79997,16 @@
     </row>
     <row r="711">
       <c r="A711" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B711" t="s" s="2">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="C711" t="s" s="2">
         <v>1116</v>
       </c>
       <c r="D711" t="s" s="2">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="E711" t="s" s="2">
         <v>75</v>
@@ -80031,13 +80028,13 @@
         <v>75</v>
       </c>
       <c r="L711" t="s" s="2">
+        <v>1283</v>
+      </c>
+      <c r="M711" t="s" s="2">
         <v>1284</v>
       </c>
-      <c r="M711" t="s" s="2">
+      <c r="N711" t="s" s="2">
         <v>1285</v>
-      </c>
-      <c r="N711" t="s" s="2">
-        <v>1286</v>
       </c>
       <c r="O711" s="2"/>
       <c r="P711" s="2"/>
@@ -80105,10 +80102,10 @@
     </row>
     <row r="712">
       <c r="A712" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B712" t="s" s="2">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="C712" t="s" s="2">
         <v>1116</v>
@@ -80139,7 +80136,7 @@
         <v>187</v>
       </c>
       <c r="M712" t="s" s="2">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="N712" t="s" s="2">
         <v>189</v>
@@ -80210,16 +80207,16 @@
     </row>
     <row r="713">
       <c r="A713" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B713" t="s" s="2">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="C713" t="s" s="2">
         <v>1116</v>
       </c>
       <c r="D713" t="s" s="2">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="E713" t="s" s="2">
         <v>75</v>
@@ -80241,10 +80238,10 @@
         <v>75</v>
       </c>
       <c r="L713" t="s" s="2">
+        <v>1290</v>
+      </c>
+      <c r="M713" t="s" s="2">
         <v>1291</v>
-      </c>
-      <c r="M713" t="s" s="2">
-        <v>1292</v>
       </c>
       <c r="N713" t="s" s="2">
         <v>994</v>
@@ -80315,13 +80312,13 @@
     </row>
     <row r="714">
       <c r="A714" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B714" t="s" s="2">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="C714" t="s" s="2">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="D714" s="2"/>
       <c r="E714" t="s" s="2">
@@ -80418,13 +80415,13 @@
     </row>
     <row r="715">
       <c r="A715" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B715" t="s" s="2">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="C715" t="s" s="2">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="D715" s="2"/>
       <c r="E715" t="s" s="2">
@@ -80521,13 +80518,13 @@
     </row>
     <row r="716">
       <c r="A716" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B716" t="s" s="2">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="C716" t="s" s="2">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="D716" s="2"/>
       <c r="E716" t="s" s="2">
@@ -80626,13 +80623,13 @@
     </row>
     <row r="717">
       <c r="A717" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B717" t="s" s="2">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="C717" t="s" s="2">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="D717" s="2"/>
       <c r="E717" t="s" s="2">
@@ -80655,7 +80652,7 @@
         <v>75</v>
       </c>
       <c r="L717" t="s" s="2">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="M717" t="s" s="2">
         <v>1007</v>
@@ -80729,7 +80726,7 @@
     </row>
     <row r="718">
       <c r="A718" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B718" t="s" s="2">
         <v>1122</v>
@@ -80832,7 +80829,7 @@
     </row>
     <row r="719">
       <c r="A719" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B719" t="s" s="2">
         <v>1123</v>
@@ -80933,7 +80930,7 @@
     </row>
     <row r="720">
       <c r="A720" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B720" t="s" s="2">
         <v>1126</v>
@@ -80964,10 +80961,10 @@
         <v>75</v>
       </c>
       <c r="L720" t="s" s="2">
+        <v>1297</v>
+      </c>
+      <c r="M720" t="s" s="2">
         <v>1298</v>
-      </c>
-      <c r="M720" t="s" s="2">
-        <v>1299</v>
       </c>
       <c r="N720" t="s" s="2">
         <v>196</v>
@@ -81038,7 +81035,7 @@
     </row>
     <row r="721">
       <c r="A721" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B721" t="s" s="2">
         <v>1129</v>
@@ -81072,7 +81069,7 @@
         <v>206</v>
       </c>
       <c r="M721" t="s" s="2">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="N721" t="s" s="2">
         <v>196</v>
@@ -81143,7 +81140,7 @@
     </row>
     <row r="722">
       <c r="A722" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B722" t="s" s="2">
         <v>1131</v>
@@ -81175,7 +81172,7 @@
         <v>159</v>
       </c>
       <c r="M722" t="s" s="2">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="N722" t="s" s="2">
         <v>1133</v>
@@ -81248,7 +81245,7 @@
     </row>
     <row r="723">
       <c r="A723" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B723" t="s" s="2">
         <v>1137</v>
@@ -81280,7 +81277,7 @@
         <v>159</v>
       </c>
       <c r="M723" t="s" s="2">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="N723" t="s" s="2">
         <v>1139</v>
@@ -81355,7 +81352,7 @@
     </row>
     <row r="724">
       <c r="A724" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B724" t="s" s="2">
         <v>1145</v>
@@ -81387,7 +81384,7 @@
         <v>98</v>
       </c>
       <c r="M724" t="s" s="2">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="N724" t="s" s="2">
         <v>1147</v>
@@ -81460,7 +81457,7 @@
     </row>
     <row r="725">
       <c r="A725" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B725" t="s" s="2">
         <v>1150</v>
@@ -81492,7 +81489,7 @@
         <v>221</v>
       </c>
       <c r="M725" t="s" s="2">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="N725" t="s" s="2">
         <v>1152</v>
@@ -81511,7 +81508,7 @@
         <v>75</v>
       </c>
       <c r="T725" t="s" s="2">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="U725" t="s" s="2">
         <v>75</v>
@@ -81565,7 +81562,7 @@
     </row>
     <row r="726">
       <c r="A726" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B726" t="s" s="2">
         <v>1157</v>
@@ -81672,7 +81669,7 @@
     </row>
     <row r="727">
       <c r="A727" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B727" t="s" s="2">
         <v>1162</v>
@@ -81775,7 +81772,7 @@
     </row>
     <row r="728">
       <c r="A728" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B728" t="s" s="2">
         <v>1166</v>
@@ -81807,7 +81804,7 @@
         <v>356</v>
       </c>
       <c r="M728" t="s" s="2">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="N728" t="s" s="2">
         <v>1168</v>
@@ -81882,7 +81879,7 @@
     </row>
     <row r="729">
       <c r="A729" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B729" t="s" s="2">
         <v>1171</v>
@@ -81914,7 +81911,7 @@
         <v>244</v>
       </c>
       <c r="M729" t="s" s="2">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="N729" t="s" s="2">
         <v>1175</v>
@@ -81989,13 +81986,13 @@
     </row>
     <row r="730">
       <c r="A730" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B730" t="s" s="2">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="C730" t="s" s="2">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="D730" s="2"/>
       <c r="E730" t="s" s="2">
@@ -82092,13 +82089,13 @@
     </row>
     <row r="731">
       <c r="A731" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B731" t="s" s="2">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="C731" t="s" s="2">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="D731" s="2"/>
       <c r="E731" t="s" s="2">
@@ -82197,16 +82194,16 @@
     </row>
     <row r="732">
       <c r="A732" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B732" t="s" s="2">
+        <v>1309</v>
+      </c>
+      <c r="C732" t="s" s="2">
+        <v>1308</v>
+      </c>
+      <c r="D732" t="s" s="2">
         <v>1310</v>
-      </c>
-      <c r="C732" t="s" s="2">
-        <v>1309</v>
-      </c>
-      <c r="D732" t="s" s="2">
-        <v>1311</v>
       </c>
       <c r="E732" t="s" s="2">
         <v>75</v>
@@ -82228,13 +82225,13 @@
         <v>75</v>
       </c>
       <c r="L732" t="s" s="2">
+        <v>1311</v>
+      </c>
+      <c r="M732" t="s" s="2">
         <v>1312</v>
       </c>
-      <c r="M732" t="s" s="2">
+      <c r="N732" t="s" s="2">
         <v>1313</v>
-      </c>
-      <c r="N732" t="s" s="2">
-        <v>1314</v>
       </c>
       <c r="O732" s="2"/>
       <c r="P732" s="2"/>
@@ -82302,13 +82299,13 @@
     </row>
     <row r="733">
       <c r="A733" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B733" t="s" s="2">
+        <v>1314</v>
+      </c>
+      <c r="C733" t="s" s="2">
         <v>1315</v>
-      </c>
-      <c r="C733" t="s" s="2">
-        <v>1316</v>
       </c>
       <c r="D733" s="2"/>
       <c r="E733" t="s" s="2">
@@ -82405,13 +82402,13 @@
     </row>
     <row r="734">
       <c r="A734" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B734" t="s" s="2">
+        <v>1316</v>
+      </c>
+      <c r="C734" t="s" s="2">
         <v>1317</v>
-      </c>
-      <c r="C734" t="s" s="2">
-        <v>1318</v>
       </c>
       <c r="D734" s="2"/>
       <c r="E734" t="s" s="2">
@@ -82508,13 +82505,13 @@
     </row>
     <row r="735">
       <c r="A735" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B735" t="s" s="2">
+        <v>1318</v>
+      </c>
+      <c r="C735" t="s" s="2">
         <v>1319</v>
-      </c>
-      <c r="C735" t="s" s="2">
-        <v>1320</v>
       </c>
       <c r="D735" s="2"/>
       <c r="E735" t="s" s="2">
@@ -82554,7 +82551,7 @@
       </c>
       <c r="R735" s="2"/>
       <c r="S735" t="s" s="2">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="T735" t="s" s="2">
         <v>75</v>
@@ -82613,13 +82610,13 @@
     </row>
     <row r="736">
       <c r="A736" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B736" t="s" s="2">
+        <v>1321</v>
+      </c>
+      <c r="C736" t="s" s="2">
         <v>1322</v>
-      </c>
-      <c r="C736" t="s" s="2">
-        <v>1323</v>
       </c>
       <c r="D736" s="2"/>
       <c r="E736" t="s" s="2">
@@ -82642,7 +82639,7 @@
         <v>75</v>
       </c>
       <c r="L736" t="s" s="2">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="M736" t="s" s="2">
         <v>1007</v>
@@ -82687,7 +82684,7 @@
         <v>75</v>
       </c>
       <c r="AC736" t="s" s="2">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="AD736" s="2"/>
       <c r="AE736" t="s" s="2">
@@ -82714,16 +82711,16 @@
     </row>
     <row r="737">
       <c r="A737" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B737" t="s" s="2">
+        <v>1324</v>
+      </c>
+      <c r="C737" t="s" s="2">
+        <v>1322</v>
+      </c>
+      <c r="D737" t="s" s="2">
         <v>1325</v>
-      </c>
-      <c r="C737" t="s" s="2">
-        <v>1323</v>
-      </c>
-      <c r="D737" t="s" s="2">
-        <v>1326</v>
       </c>
       <c r="E737" t="s" s="2">
         <v>75</v>
@@ -82745,7 +82742,7 @@
         <v>75</v>
       </c>
       <c r="L737" t="s" s="2">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="M737" t="s" s="2">
         <v>1007</v>
@@ -82819,13 +82816,13 @@
     </row>
     <row r="738">
       <c r="A738" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B738" t="s" s="2">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="C738" t="s" s="2">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="D738" s="2"/>
       <c r="E738" t="s" s="2">
@@ -82924,13 +82921,13 @@
     </row>
     <row r="739">
       <c r="A739" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B739" t="s" s="2">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="C739" t="s" s="2">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="D739" s="2"/>
       <c r="E739" t="s" s="2">
@@ -83029,13 +83026,13 @@
     </row>
     <row r="740">
       <c r="A740" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B740" t="s" s="2">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="C740" t="s" s="2">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D740" s="2"/>
       <c r="E740" t="s" s="2">
@@ -83134,13 +83131,13 @@
     </row>
     <row r="741">
       <c r="A741" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B741" t="s" s="2">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="C741" t="s" s="2">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="D741" s="2"/>
       <c r="E741" t="s" s="2">
@@ -83239,7 +83236,7 @@
     </row>
     <row r="742">
       <c r="A742" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B742" t="s" s="2">
         <v>1178</v>
@@ -83346,7 +83343,7 @@
     </row>
     <row r="743">
       <c r="A743" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B743" t="s" s="2">
         <v>1185</v>
@@ -83378,7 +83375,7 @@
         <v>1186</v>
       </c>
       <c r="M743" t="s" s="2">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="N743" t="s" s="2">
         <v>1188</v>
@@ -83449,7 +83446,7 @@
     </row>
     <row r="744">
       <c r="A744" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B744" t="s" s="2">
         <v>1189</v>
@@ -83481,7 +83478,7 @@
         <v>259</v>
       </c>
       <c r="M744" t="s" s="2">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="N744" t="s" s="2">
         <v>1191</v>
@@ -83554,7 +83551,7 @@
     </row>
     <row r="745">
       <c r="A745" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B745" t="s" s="2">
         <v>1194</v>
@@ -83657,7 +83654,7 @@
     </row>
     <row r="746">
       <c r="A746" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B746" t="s" s="2">
         <v>1195</v>
@@ -83762,7 +83759,7 @@
     </row>
     <row r="747">
       <c r="A747" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B747" t="s" s="2">
         <v>1196</v>
@@ -83869,7 +83866,7 @@
     </row>
     <row r="748">
       <c r="A748" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B748" t="s" s="2">
         <v>1197</v>
@@ -83976,7 +83973,7 @@
     </row>
     <row r="749">
       <c r="A749" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B749" t="s" s="2">
         <v>1204</v>
@@ -84085,7 +84082,7 @@
     </row>
     <row r="750">
       <c r="A750" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B750" t="s" s="2">
         <v>1211</v>
@@ -84190,7 +84187,7 @@
     </row>
     <row r="751">
       <c r="A751" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B751" t="s" s="2">
         <v>1215</v>
@@ -84219,10 +84216,10 @@
         <v>75</v>
       </c>
       <c r="L751" t="s" s="2">
+        <v>1333</v>
+      </c>
+      <c r="M751" t="s" s="2">
         <v>1334</v>
-      </c>
-      <c r="M751" t="s" s="2">
-        <v>1335</v>
       </c>
       <c r="N751" t="s" s="2">
         <v>1218</v>
@@ -84293,7 +84290,7 @@
     </row>
     <row r="752">
       <c r="A752" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B752" t="s" s="2">
         <v>1219</v>

--- a/nriss-patch-2/ig/all-profiles.xlsx
+++ b/nriss-patch-2/ig/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24995" uniqueCount="1335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24995" uniqueCount="1334">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T14:01:46+00:00</t>
+    <t>2026-05-27T14:12:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -789,7 +789,7 @@
     <t>DocumentReference.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole|Device|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient) &lt;&lt;contained&gt;&gt;
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole|Device|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient) &lt;&lt;contained&gt;&gt;
 </t>
   </si>
   <si>
@@ -805,7 +805,7 @@
     <t>DocumentReference.authenticator</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization) &lt;&lt;contained&gt;&gt;
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization) &lt;&lt;contained&gt;&gt;
 </t>
   </si>
   <si>
@@ -3893,10 +3893,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization)
-</t>
-  </si>
-  <si>
     <t>Relationships to other documents</t>
   </si>
   <si>
@@ -4066,10 +4062,6 @@
     <t>List.extension:PDSmintendedRecipient.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization) &lt;&lt;contained&gt;&gt;
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">Identifier {https://profiles.ihe.net/ITI/MHD/StructureDefinition/IHE.MHD.SubmissionSetUniqueIdIdentifier}
 </t>
   </si>
@@ -4101,6 +4093,10 @@
   </si>
   <si>
     <t>Représente la date et heure de soumission.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole|Device|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient) &lt;&lt;contained&gt;&gt;
+</t>
   </si>
   <si>
     <t>Représente l'auteur du lot de soumission. Si l'auteur est une organisation, utiliser l'extension authorOrg. Si l’auteur est une personne physique ou un dispositif, utiliser l’attribut source.reference .</t>
@@ -5663,7 +5659,7 @@
         <v>2</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="174">
@@ -5671,7 +5667,7 @@
         <v>4</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="175">
@@ -5687,7 +5683,7 @@
         <v>8</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="177">
@@ -5695,7 +5691,7 @@
         <v>10</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="178">
@@ -5749,7 +5745,7 @@
         <v>23</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>1257</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="185">
@@ -5793,7 +5789,7 @@
         <v>33</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="191">
@@ -73754,7 +73750,7 @@
         <v>75</v>
       </c>
       <c r="L651" t="s" s="2">
-        <v>1243</v>
+        <v>1006</v>
       </c>
       <c r="M651" t="s" s="2">
         <v>250</v>
@@ -73967,10 +73963,10 @@
         <v>259</v>
       </c>
       <c r="M653" t="s" s="2">
+        <v>1243</v>
+      </c>
+      <c r="N653" t="s" s="2">
         <v>1244</v>
-      </c>
-      <c r="N653" t="s" s="2">
-        <v>1245</v>
       </c>
       <c r="O653" t="s" s="2">
         <v>262</v>
@@ -74387,7 +74383,7 @@
         <v>159</v>
       </c>
       <c r="M657" t="s" s="2">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="N657" t="s" s="2">
         <v>274</v>
@@ -74492,7 +74488,7 @@
         <v>279</v>
       </c>
       <c r="M658" t="s" s="2">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="N658" t="s" s="2">
         <v>281</v>
@@ -74809,7 +74805,7 @@
         <v>259</v>
       </c>
       <c r="M661" t="s" s="2">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="N661" t="s" s="2">
         <v>296</v>
@@ -75748,7 +75744,7 @@
         <v>321</v>
       </c>
       <c r="M670" t="s" s="2">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="N670" t="s" s="2">
         <v>323</v>
@@ -75855,7 +75851,7 @@
         <v>328</v>
       </c>
       <c r="M671" t="s" s="2">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="N671" t="s" s="2">
         <v>330</v>
@@ -76281,7 +76277,7 @@
         <v>356</v>
       </c>
       <c r="M675" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="N675" t="s" s="2">
         <v>358</v>
@@ -77284,7 +77280,7 @@
         <v>75</v>
       </c>
       <c r="AK684" t="s" s="2">
-        <v>1252</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="685">
@@ -77389,7 +77385,7 @@
         <v>75</v>
       </c>
       <c r="AK685" t="s" s="2">
-        <v>1252</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="686">
@@ -77602,7 +77598,7 @@
     </row>
     <row r="688">
       <c r="A688" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B688" t="s" s="2">
         <v>1099</v>
@@ -77705,7 +77701,7 @@
     </row>
     <row r="689">
       <c r="A689" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B689" t="s" s="2">
         <v>1101</v>
@@ -77810,7 +77806,7 @@
     </row>
     <row r="690">
       <c r="A690" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B690" t="s" s="2">
         <v>1102</v>
@@ -77913,7 +77909,7 @@
     </row>
     <row r="691">
       <c r="A691" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B691" t="s" s="2">
         <v>1103</v>
@@ -78016,7 +78012,7 @@
     </row>
     <row r="692">
       <c r="A692" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B692" t="s" s="2">
         <v>1104</v>
@@ -78121,7 +78117,7 @@
     </row>
     <row r="693">
       <c r="A693" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B693" t="s" s="2">
         <v>1105</v>
@@ -78226,7 +78222,7 @@
     </row>
     <row r="694">
       <c r="A694" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B694" t="s" s="2">
         <v>1106</v>
@@ -78331,7 +78327,7 @@
     </row>
     <row r="695">
       <c r="A695" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B695" t="s" s="2">
         <v>1107</v>
@@ -78436,7 +78432,7 @@
     </row>
     <row r="696">
       <c r="A696" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B696" t="s" s="2">
         <v>1108</v>
@@ -78541,7 +78537,7 @@
     </row>
     <row r="697">
       <c r="A697" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B697" t="s" s="2">
         <v>1109</v>
@@ -78646,7 +78642,7 @@
     </row>
     <row r="698">
       <c r="A698" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B698" t="s" s="2">
         <v>1110</v>
@@ -78751,7 +78747,7 @@
     </row>
     <row r="699">
       <c r="A699" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B699" t="s" s="2">
         <v>1111</v>
@@ -78856,7 +78852,7 @@
     </row>
     <row r="700">
       <c r="A700" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B700" t="s" s="2">
         <v>1112</v>
@@ -78961,7 +78957,7 @@
     </row>
     <row r="701">
       <c r="A701" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B701" t="s" s="2">
         <v>1113</v>
@@ -79066,7 +79062,7 @@
     </row>
     <row r="702">
       <c r="A702" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B702" t="s" s="2">
         <v>1114</v>
@@ -79098,7 +79094,7 @@
         <v>176</v>
       </c>
       <c r="M702" t="s" s="2">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="N702" t="s" s="2">
         <v>178</v>
@@ -79171,7 +79167,7 @@
     </row>
     <row r="703">
       <c r="A703" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B703" t="s" s="2">
         <v>1116</v>
@@ -79185,7 +79181,7 @@
       </c>
       <c r="F703" s="2"/>
       <c r="G703" t="s" s="2">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="H703" t="s" s="2">
         <v>77</v>
@@ -79272,7 +79268,7 @@
     </row>
     <row r="704">
       <c r="A704" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B704" t="s" s="2">
         <v>1117</v>
@@ -79306,7 +79302,7 @@
         <v>1119</v>
       </c>
       <c r="M704" t="s" s="2">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="N704" t="s" s="2">
         <v>1121</v>
@@ -79372,18 +79368,18 @@
         <v>190</v>
       </c>
       <c r="AK704" t="s" s="2">
-        <v>1262</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B705" t="s" s="2">
+        <v>1262</v>
+      </c>
+      <c r="C705" t="s" s="2">
         <v>1263</v>
-      </c>
-      <c r="C705" t="s" s="2">
-        <v>1264</v>
       </c>
       <c r="D705" s="2"/>
       <c r="E705" t="s" s="2">
@@ -79480,13 +79476,13 @@
     </row>
     <row r="706">
       <c r="A706" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B706" t="s" s="2">
+        <v>1264</v>
+      </c>
+      <c r="C706" t="s" s="2">
         <v>1265</v>
-      </c>
-      <c r="C706" t="s" s="2">
-        <v>1266</v>
       </c>
       <c r="D706" s="2"/>
       <c r="E706" t="s" s="2">
@@ -79583,13 +79579,13 @@
     </row>
     <row r="707">
       <c r="A707" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B707" t="s" s="2">
+        <v>1266</v>
+      </c>
+      <c r="C707" t="s" s="2">
         <v>1267</v>
-      </c>
-      <c r="C707" t="s" s="2">
-        <v>1268</v>
       </c>
       <c r="D707" s="2"/>
       <c r="E707" t="s" s="2">
@@ -79629,7 +79625,7 @@
       </c>
       <c r="R707" s="2"/>
       <c r="S707" t="s" s="2">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="T707" t="s" s="2">
         <v>75</v>
@@ -79688,13 +79684,13 @@
     </row>
     <row r="708">
       <c r="A708" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B708" t="s" s="2">
+        <v>1269</v>
+      </c>
+      <c r="C708" t="s" s="2">
         <v>1270</v>
-      </c>
-      <c r="C708" t="s" s="2">
-        <v>1271</v>
       </c>
       <c r="D708" s="2"/>
       <c r="E708" t="s" s="2">
@@ -79754,13 +79750,13 @@
       </c>
       <c r="Z708" s="2"/>
       <c r="AA708" t="s" s="2">
+        <v>1271</v>
+      </c>
+      <c r="AB708" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC708" t="s" s="2">
         <v>1272</v>
-      </c>
-      <c r="AB708" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC708" t="s" s="2">
-        <v>1273</v>
       </c>
       <c r="AD708" s="2"/>
       <c r="AE708" t="s" s="2">
@@ -79787,16 +79783,16 @@
     </row>
     <row r="709">
       <c r="A709" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B709" t="s" s="2">
+        <v>1273</v>
+      </c>
+      <c r="C709" t="s" s="2">
+        <v>1270</v>
+      </c>
+      <c r="D709" t="s" s="2">
         <v>1274</v>
-      </c>
-      <c r="C709" t="s" s="2">
-        <v>1271</v>
-      </c>
-      <c r="D709" t="s" s="2">
-        <v>1275</v>
       </c>
       <c r="E709" t="s" s="2">
         <v>75</v>
@@ -79892,16 +79888,16 @@
     </row>
     <row r="710">
       <c r="A710" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B710" t="s" s="2">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="C710" t="s" s="2">
         <v>1116</v>
       </c>
       <c r="D710" t="s" s="2">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="E710" t="s" s="2">
         <v>75</v>
@@ -79923,13 +79919,13 @@
         <v>75</v>
       </c>
       <c r="L710" t="s" s="2">
+        <v>1277</v>
+      </c>
+      <c r="M710" t="s" s="2">
         <v>1278</v>
       </c>
-      <c r="M710" t="s" s="2">
+      <c r="N710" t="s" s="2">
         <v>1279</v>
-      </c>
-      <c r="N710" t="s" s="2">
-        <v>1280</v>
       </c>
       <c r="O710" s="2"/>
       <c r="P710" s="2"/>
@@ -79997,16 +79993,16 @@
     </row>
     <row r="711">
       <c r="A711" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B711" t="s" s="2">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="C711" t="s" s="2">
         <v>1116</v>
       </c>
       <c r="D711" t="s" s="2">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="E711" t="s" s="2">
         <v>75</v>
@@ -80028,13 +80024,13 @@
         <v>75</v>
       </c>
       <c r="L711" t="s" s="2">
+        <v>1282</v>
+      </c>
+      <c r="M711" t="s" s="2">
         <v>1283</v>
       </c>
-      <c r="M711" t="s" s="2">
+      <c r="N711" t="s" s="2">
         <v>1284</v>
-      </c>
-      <c r="N711" t="s" s="2">
-        <v>1285</v>
       </c>
       <c r="O711" s="2"/>
       <c r="P711" s="2"/>
@@ -80102,10 +80098,10 @@
     </row>
     <row r="712">
       <c r="A712" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B712" t="s" s="2">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="C712" t="s" s="2">
         <v>1116</v>
@@ -80136,7 +80132,7 @@
         <v>187</v>
       </c>
       <c r="M712" t="s" s="2">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="N712" t="s" s="2">
         <v>189</v>
@@ -80207,16 +80203,16 @@
     </row>
     <row r="713">
       <c r="A713" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B713" t="s" s="2">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="C713" t="s" s="2">
         <v>1116</v>
       </c>
       <c r="D713" t="s" s="2">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="E713" t="s" s="2">
         <v>75</v>
@@ -80238,10 +80234,10 @@
         <v>75</v>
       </c>
       <c r="L713" t="s" s="2">
+        <v>1289</v>
+      </c>
+      <c r="M713" t="s" s="2">
         <v>1290</v>
-      </c>
-      <c r="M713" t="s" s="2">
-        <v>1291</v>
       </c>
       <c r="N713" t="s" s="2">
         <v>994</v>
@@ -80312,13 +80308,13 @@
     </row>
     <row r="714">
       <c r="A714" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B714" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="C714" t="s" s="2">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="D714" s="2"/>
       <c r="E714" t="s" s="2">
@@ -80415,13 +80411,13 @@
     </row>
     <row r="715">
       <c r="A715" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B715" t="s" s="2">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="C715" t="s" s="2">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="D715" s="2"/>
       <c r="E715" t="s" s="2">
@@ -80518,13 +80514,13 @@
     </row>
     <row r="716">
       <c r="A716" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B716" t="s" s="2">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="C716" t="s" s="2">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="D716" s="2"/>
       <c r="E716" t="s" s="2">
@@ -80623,13 +80619,13 @@
     </row>
     <row r="717">
       <c r="A717" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B717" t="s" s="2">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="C717" t="s" s="2">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="D717" s="2"/>
       <c r="E717" t="s" s="2">
@@ -80652,7 +80648,7 @@
         <v>75</v>
       </c>
       <c r="L717" t="s" s="2">
-        <v>1296</v>
+        <v>249</v>
       </c>
       <c r="M717" t="s" s="2">
         <v>1007</v>
@@ -80726,7 +80722,7 @@
     </row>
     <row r="718">
       <c r="A718" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B718" t="s" s="2">
         <v>1122</v>
@@ -80829,7 +80825,7 @@
     </row>
     <row r="719">
       <c r="A719" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B719" t="s" s="2">
         <v>1123</v>
@@ -80930,7 +80926,7 @@
     </row>
     <row r="720">
       <c r="A720" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B720" t="s" s="2">
         <v>1126</v>
@@ -80961,10 +80957,10 @@
         <v>75</v>
       </c>
       <c r="L720" t="s" s="2">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="M720" t="s" s="2">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="N720" t="s" s="2">
         <v>196</v>
@@ -81035,7 +81031,7 @@
     </row>
     <row r="721">
       <c r="A721" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B721" t="s" s="2">
         <v>1129</v>
@@ -81069,7 +81065,7 @@
         <v>206</v>
       </c>
       <c r="M721" t="s" s="2">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="N721" t="s" s="2">
         <v>196</v>
@@ -81140,7 +81136,7 @@
     </row>
     <row r="722">
       <c r="A722" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B722" t="s" s="2">
         <v>1131</v>
@@ -81172,7 +81168,7 @@
         <v>159</v>
       </c>
       <c r="M722" t="s" s="2">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="N722" t="s" s="2">
         <v>1133</v>
@@ -81245,7 +81241,7 @@
     </row>
     <row r="723">
       <c r="A723" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B723" t="s" s="2">
         <v>1137</v>
@@ -81277,7 +81273,7 @@
         <v>159</v>
       </c>
       <c r="M723" t="s" s="2">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="N723" t="s" s="2">
         <v>1139</v>
@@ -81352,7 +81348,7 @@
     </row>
     <row r="724">
       <c r="A724" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B724" t="s" s="2">
         <v>1145</v>
@@ -81384,7 +81380,7 @@
         <v>98</v>
       </c>
       <c r="M724" t="s" s="2">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="N724" t="s" s="2">
         <v>1147</v>
@@ -81457,7 +81453,7 @@
     </row>
     <row r="725">
       <c r="A725" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B725" t="s" s="2">
         <v>1150</v>
@@ -81489,7 +81485,7 @@
         <v>221</v>
       </c>
       <c r="M725" t="s" s="2">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="N725" t="s" s="2">
         <v>1152</v>
@@ -81508,7 +81504,7 @@
         <v>75</v>
       </c>
       <c r="T725" t="s" s="2">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="U725" t="s" s="2">
         <v>75</v>
@@ -81562,7 +81558,7 @@
     </row>
     <row r="726">
       <c r="A726" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B726" t="s" s="2">
         <v>1157</v>
@@ -81669,7 +81665,7 @@
     </row>
     <row r="727">
       <c r="A727" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B727" t="s" s="2">
         <v>1162</v>
@@ -81772,7 +81768,7 @@
     </row>
     <row r="728">
       <c r="A728" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B728" t="s" s="2">
         <v>1166</v>
@@ -81804,7 +81800,7 @@
         <v>356</v>
       </c>
       <c r="M728" t="s" s="2">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="N728" t="s" s="2">
         <v>1168</v>
@@ -81879,7 +81875,7 @@
     </row>
     <row r="729">
       <c r="A729" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B729" t="s" s="2">
         <v>1171</v>
@@ -81908,10 +81904,10 @@
         <v>85</v>
       </c>
       <c r="L729" t="s" s="2">
-        <v>244</v>
+        <v>1304</v>
       </c>
       <c r="M729" t="s" s="2">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="N729" t="s" s="2">
         <v>1175</v>
@@ -81986,13 +81982,13 @@
     </row>
     <row r="730">
       <c r="A730" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B730" t="s" s="2">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="C730" t="s" s="2">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="D730" s="2"/>
       <c r="E730" t="s" s="2">
@@ -82089,13 +82085,13 @@
     </row>
     <row r="731">
       <c r="A731" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B731" t="s" s="2">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="C731" t="s" s="2">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="D731" s="2"/>
       <c r="E731" t="s" s="2">
@@ -82194,16 +82190,16 @@
     </row>
     <row r="732">
       <c r="A732" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B732" t="s" s="2">
+        <v>1308</v>
+      </c>
+      <c r="C732" t="s" s="2">
+        <v>1307</v>
+      </c>
+      <c r="D732" t="s" s="2">
         <v>1309</v>
-      </c>
-      <c r="C732" t="s" s="2">
-        <v>1308</v>
-      </c>
-      <c r="D732" t="s" s="2">
-        <v>1310</v>
       </c>
       <c r="E732" t="s" s="2">
         <v>75</v>
@@ -82225,13 +82221,13 @@
         <v>75</v>
       </c>
       <c r="L732" t="s" s="2">
+        <v>1310</v>
+      </c>
+      <c r="M732" t="s" s="2">
         <v>1311</v>
       </c>
-      <c r="M732" t="s" s="2">
+      <c r="N732" t="s" s="2">
         <v>1312</v>
-      </c>
-      <c r="N732" t="s" s="2">
-        <v>1313</v>
       </c>
       <c r="O732" s="2"/>
       <c r="P732" s="2"/>
@@ -82299,13 +82295,13 @@
     </row>
     <row r="733">
       <c r="A733" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B733" t="s" s="2">
+        <v>1313</v>
+      </c>
+      <c r="C733" t="s" s="2">
         <v>1314</v>
-      </c>
-      <c r="C733" t="s" s="2">
-        <v>1315</v>
       </c>
       <c r="D733" s="2"/>
       <c r="E733" t="s" s="2">
@@ -82402,13 +82398,13 @@
     </row>
     <row r="734">
       <c r="A734" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B734" t="s" s="2">
+        <v>1315</v>
+      </c>
+      <c r="C734" t="s" s="2">
         <v>1316</v>
-      </c>
-      <c r="C734" t="s" s="2">
-        <v>1317</v>
       </c>
       <c r="D734" s="2"/>
       <c r="E734" t="s" s="2">
@@ -82505,13 +82501,13 @@
     </row>
     <row r="735">
       <c r="A735" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B735" t="s" s="2">
+        <v>1317</v>
+      </c>
+      <c r="C735" t="s" s="2">
         <v>1318</v>
-      </c>
-      <c r="C735" t="s" s="2">
-        <v>1319</v>
       </c>
       <c r="D735" s="2"/>
       <c r="E735" t="s" s="2">
@@ -82551,7 +82547,7 @@
       </c>
       <c r="R735" s="2"/>
       <c r="S735" t="s" s="2">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="T735" t="s" s="2">
         <v>75</v>
@@ -82610,13 +82606,13 @@
     </row>
     <row r="736">
       <c r="A736" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B736" t="s" s="2">
+        <v>1320</v>
+      </c>
+      <c r="C736" t="s" s="2">
         <v>1321</v>
-      </c>
-      <c r="C736" t="s" s="2">
-        <v>1322</v>
       </c>
       <c r="D736" s="2"/>
       <c r="E736" t="s" s="2">
@@ -82639,7 +82635,7 @@
         <v>75</v>
       </c>
       <c r="L736" t="s" s="2">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="M736" t="s" s="2">
         <v>1007</v>
@@ -82684,7 +82680,7 @@
         <v>75</v>
       </c>
       <c r="AC736" t="s" s="2">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="AD736" s="2"/>
       <c r="AE736" t="s" s="2">
@@ -82711,16 +82707,16 @@
     </row>
     <row r="737">
       <c r="A737" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B737" t="s" s="2">
+        <v>1323</v>
+      </c>
+      <c r="C737" t="s" s="2">
+        <v>1321</v>
+      </c>
+      <c r="D737" t="s" s="2">
         <v>1324</v>
-      </c>
-      <c r="C737" t="s" s="2">
-        <v>1322</v>
-      </c>
-      <c r="D737" t="s" s="2">
-        <v>1325</v>
       </c>
       <c r="E737" t="s" s="2">
         <v>75</v>
@@ -82742,7 +82738,7 @@
         <v>75</v>
       </c>
       <c r="L737" t="s" s="2">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="M737" t="s" s="2">
         <v>1007</v>
@@ -82816,13 +82812,13 @@
     </row>
     <row r="738">
       <c r="A738" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B738" t="s" s="2">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="C738" t="s" s="2">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="D738" s="2"/>
       <c r="E738" t="s" s="2">
@@ -82921,13 +82917,13 @@
     </row>
     <row r="739">
       <c r="A739" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B739" t="s" s="2">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="C739" t="s" s="2">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="D739" s="2"/>
       <c r="E739" t="s" s="2">
@@ -83026,13 +83022,13 @@
     </row>
     <row r="740">
       <c r="A740" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B740" t="s" s="2">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="C740" t="s" s="2">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="D740" s="2"/>
       <c r="E740" t="s" s="2">
@@ -83131,13 +83127,13 @@
     </row>
     <row r="741">
       <c r="A741" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B741" t="s" s="2">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="C741" t="s" s="2">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D741" s="2"/>
       <c r="E741" t="s" s="2">
@@ -83236,7 +83232,7 @@
     </row>
     <row r="742">
       <c r="A742" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B742" t="s" s="2">
         <v>1178</v>
@@ -83343,7 +83339,7 @@
     </row>
     <row r="743">
       <c r="A743" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B743" t="s" s="2">
         <v>1185</v>
@@ -83375,7 +83371,7 @@
         <v>1186</v>
       </c>
       <c r="M743" t="s" s="2">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="N743" t="s" s="2">
         <v>1188</v>
@@ -83446,7 +83442,7 @@
     </row>
     <row r="744">
       <c r="A744" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B744" t="s" s="2">
         <v>1189</v>
@@ -83478,7 +83474,7 @@
         <v>259</v>
       </c>
       <c r="M744" t="s" s="2">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="N744" t="s" s="2">
         <v>1191</v>
@@ -83551,7 +83547,7 @@
     </row>
     <row r="745">
       <c r="A745" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B745" t="s" s="2">
         <v>1194</v>
@@ -83654,7 +83650,7 @@
     </row>
     <row r="746">
       <c r="A746" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B746" t="s" s="2">
         <v>1195</v>
@@ -83759,7 +83755,7 @@
     </row>
     <row r="747">
       <c r="A747" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B747" t="s" s="2">
         <v>1196</v>
@@ -83866,7 +83862,7 @@
     </row>
     <row r="748">
       <c r="A748" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B748" t="s" s="2">
         <v>1197</v>
@@ -83973,7 +83969,7 @@
     </row>
     <row r="749">
       <c r="A749" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B749" t="s" s="2">
         <v>1204</v>
@@ -84082,7 +84078,7 @@
     </row>
     <row r="750">
       <c r="A750" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B750" t="s" s="2">
         <v>1211</v>
@@ -84187,7 +84183,7 @@
     </row>
     <row r="751">
       <c r="A751" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B751" t="s" s="2">
         <v>1215</v>
@@ -84216,10 +84212,10 @@
         <v>75</v>
       </c>
       <c r="L751" t="s" s="2">
+        <v>1332</v>
+      </c>
+      <c r="M751" t="s" s="2">
         <v>1333</v>
-      </c>
-      <c r="M751" t="s" s="2">
-        <v>1334</v>
       </c>
       <c r="N751" t="s" s="2">
         <v>1218</v>
@@ -84290,7 +84286,7 @@
     </row>
     <row r="752">
       <c r="A752" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B752" t="s" s="2">
         <v>1219</v>
